--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487195_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487195_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9811</v>
+        <v>4.2965</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0832</v>
+        <v>5.5593</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1022</v>
+        <v>-1.2628</v>
       </c>
       <c r="G2" t="n">
         <v>3.4753</v>
@@ -610,13 +610,13 @@
         <v>1.5441</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4311</v>
+        <v>0.7466</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0888</v>
+        <v>0.5649</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3423</v>
+        <v>0.1817</v>
       </c>
       <c r="V2" t="n">
         <v>3.3558</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4313</v>
+        <v>2.6401</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1078</v>
+        <v>0.2268</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3235</v>
+        <v>2.4133</v>
       </c>
       <c r="G3" t="n">
         <v>1.4812</v>
@@ -688,13 +688,13 @@
         <v>1.9301</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8077</v>
+        <v>0.0165</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5221</v>
+        <v>-0.4032</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3298</v>
+        <v>0.4197</v>
       </c>
       <c r="V3" t="n">
         <v>0.3704</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9114</v>
+        <v>2.1315</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1434</v>
+        <v>0.2029</v>
       </c>
       <c r="F4" t="n">
-        <v>1.768</v>
+        <v>1.9286</v>
       </c>
       <c r="G4" t="n">
         <v>0.9855</v>
@@ -766,13 +766,13 @@
         <v>1.158</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6954</v>
+        <v>-0.4752</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4019</v>
+        <v>-0.3424</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2935</v>
+        <v>-0.1329</v>
       </c>
       <c r="V4" t="n">
         <v>0.6562</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.308</v>
+        <v>1.8137</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9834000000000001</v>
+        <v>1.2213</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3246</v>
+        <v>0.5923</v>
       </c>
       <c r="G5" t="n">
         <v>1.3556</v>
@@ -844,13 +844,13 @@
         <v>2.1231</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0549</v>
+        <v>-0.5493</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3291</v>
+        <v>-0.0912</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7258</v>
+        <v>-0.4581</v>
       </c>
       <c r="V5" t="n">
         <v>0.0422</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6055</v>
+        <v>1.125</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9828</v>
+        <v>-1.4633</v>
       </c>
       <c r="F6" t="n">
         <v>2.5883</v>
@@ -922,10 +922,10 @@
         <v>1.5441</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7866</v>
+        <v>-0.267</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8778</v>
+        <v>-0.3582</v>
       </c>
       <c r="U6" t="n">
         <v>0.0912</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2873</v>
+        <v>0.1589</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0693</v>
+        <v>-0.6499</v>
       </c>
       <c r="F7" t="n">
-        <v>0.782</v>
+        <v>0.8088</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0282</v>
@@ -1000,13 +1000,13 @@
         <v>1.5441</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0358</v>
+        <v>-0.5896</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0113</v>
+        <v>-0.5919</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0245</v>
+        <v>0.0023</v>
       </c>
       <c r="V7" t="n">
         <v>2.1278</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4941</v>
+        <v>0.1127</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1709</v>
+        <v>-0.7426</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2342</v>
@@ -1078,13 +1078,13 @@
         <v>1.9301</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4528</v>
+        <v>-0.8461</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5671</v>
+        <v>-0.3886</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8857</v>
+        <v>-0.4574</v>
       </c>
       <c r="V8" t="n">
         <v>1.228</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8818</v>
+        <v>-0.9225</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.047</v>
+        <v>-0.0876</v>
       </c>
       <c r="F9" t="n">
         <v>-0.8348</v>
@@ -1156,10 +1156,10 @@
         <v>0.386</v>
       </c>
       <c r="S9" t="n">
-        <v>0.074</v>
+        <v>0.0334</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0132</v>
+        <v>-0.0274</v>
       </c>
       <c r="U9" t="n">
         <v>0.0608</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8498</v>
+        <v>-1.2638</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1933</v>
+        <v>-1.4735</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3435</v>
+        <v>0.2097</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6184</v>
@@ -1234,13 +1234,13 @@
         <v>1.3511</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6524</v>
+        <v>-0.0664</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8183</v>
+        <v>-0.0985</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1659</v>
+        <v>0.032</v>
       </c>
       <c r="V10" t="n">
         <v>1.228</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4034</v>
+        <v>-1.9622</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2399</v>
+        <v>-1.0396</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1635</v>
+        <v>-0.9226</v>
       </c>
       <c r="G11" t="n">
         <v>-0.7267</v>
@@ -1312,13 +1312,13 @@
         <v>0.965</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4488</v>
+        <v>-0.0076</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4759</v>
+        <v>-0.2756</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0271</v>
+        <v>0.268</v>
       </c>
       <c r="V11" t="n">
         <v>-1.228</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5053</v>
+        <v>-2.1246</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8435</v>
+        <v>-0.543</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6619</v>
+        <v>-1.5816</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0539</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4515</v>
+        <v>-0.0707</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.238</v>
+        <v>0.0625</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2135</v>
+        <v>-0.1332</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.8156</v>
+        <v>6.005300000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6189</v>
+        <v>2.808700000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>3.196599999999999</v>
+        <v>3.1966</v>
       </c>
       <c r="G13" t="n">
         <v>-4.1049</v>
@@ -1468,10 +1468,10 @@
         <v>14.4757</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.2654</v>
+        <v>-2.0754</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.1395</v>
+        <v>-1.9496</v>
       </c>
       <c r="U13" t="n">
         <v>-0.1258999999999998</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. QUINCY-JONES</t>
+          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.2606</v>
+        <v>5.6133</v>
       </c>
       <c r="E14" t="n">
-        <v>5.0091</v>
+        <v>5.7716</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2515</v>
+        <v>-0.1582</v>
       </c>
       <c r="G14" t="n">
-        <v>5.0671</v>
+        <v>6.1634</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5705</v>
+        <v>2.4405</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4966</v>
+        <v>3.7229</v>
       </c>
       <c r="J14" t="n">
-        <v>5.6876</v>
+        <v>7.932</v>
       </c>
       <c r="K14" t="n">
-        <v>5.5005</v>
+        <v>4.978</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1871</v>
+        <v>2.9539</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.6205000000000001</v>
+        <v>-1.7686</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.93</v>
+        <v>-2.5376</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3095</v>
+        <v>0.769</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.579</v>
+        <v>-0.386</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.8951</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3161</v>
+        <v>2.5091</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1409</v>
+        <v>0.8606</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3167</v>
+        <v>-0.1229</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8242</v>
+        <v>0.9835</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3684</v>
+        <v>-1.0246</v>
       </c>
       <c r="W14" t="n">
-        <v>0.8999</v>
+        <v>0.8576</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2682</v>
+        <v>-1.8822</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
+          <t>A. QUINCY-JONES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.7858</v>
+        <v>5.2519</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9705</v>
+        <v>4.1078</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1847</v>
+        <v>1.1441</v>
       </c>
       <c r="G15" t="n">
-        <v>6.1634</v>
+        <v>5.0671</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4405</v>
+        <v>3.5705</v>
       </c>
       <c r="I15" t="n">
-        <v>3.7229</v>
+        <v>1.4966</v>
       </c>
       <c r="J15" t="n">
-        <v>7.932</v>
+        <v>5.6876</v>
       </c>
       <c r="K15" t="n">
-        <v>4.978</v>
+        <v>5.5005</v>
       </c>
       <c r="L15" t="n">
-        <v>2.9539</v>
+        <v>0.1871</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7686</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.5376</v>
+        <v>-1.93</v>
       </c>
       <c r="O15" t="n">
-        <v>0.769</v>
+        <v>1.3095</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.386</v>
+        <v>-0.579</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.8951</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5091</v>
+        <v>2.3161</v>
       </c>
       <c r="S15" t="n">
-        <v>0.033</v>
+        <v>1.1323</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.924</v>
+        <v>0.4155</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9571</v>
+        <v>0.7168</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0246</v>
+        <v>-0.3684</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8576</v>
+        <v>0.8999</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8822</v>
+        <v>-1.2682</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8529</v>
+        <v>0.7593</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0608</v>
+        <v>-0.1395</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7921</v>
+        <v>0.8988</v>
       </c>
       <c r="G16" t="n">
         <v>0.7184</v>
@@ -1702,13 +1702,13 @@
         <v>0.965</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8137</v>
+        <v>0.7201</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0132</v>
+        <v>-0.187</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8004</v>
+        <v>0.9072</v>
       </c>
       <c r="V16" t="n">
         <v>0.2859</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7758</v>
+        <v>-0.2952</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1442</v>
+        <v>-0.7437</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3685</v>
+        <v>0.4485</v>
       </c>
       <c r="G17" t="n">
         <v>-1.2018</v>
@@ -1780,13 +1780,13 @@
         <v>1.3511</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5989</v>
+        <v>-0.1183</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9967</v>
+        <v>-0.5962</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3979</v>
+        <v>0.4779</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3261</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9647</v>
+        <v>-0.6642</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="F18" t="n">
         <v>-0.0034</v>
@@ -1858,10 +1858,10 @@
         <v>0.193</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.386</v>
+        <v>-0.0856</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4164</v>
+        <v>-0.116</v>
       </c>
       <c r="U18" t="n">
         <v>0.0304</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2176</v>
+        <v>-2.4248</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0052</v>
+        <v>-1.1054</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2123</v>
+        <v>-1.3194</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4973</v>
@@ -1936,13 +1936,13 @@
         <v>0.193</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3146</v>
+        <v>0.1074</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1917</v>
+        <v>0.0916</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1229</v>
+        <v>0.0159</v>
       </c>
       <c r="V19" t="n">
         <v>-1.228</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9575</v>
+        <v>-3.4711</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5084</v>
+        <v>-1.2094</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4491</v>
+        <v>-2.2617</v>
       </c>
       <c r="G20" t="n">
         <v>0.2718</v>
@@ -2014,13 +2014,13 @@
         <v>1.9301</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8653</v>
+        <v>0.3517</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0656</v>
+        <v>0.3646</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2003</v>
+        <v>-0.0129</v>
       </c>
       <c r="V20" t="n">
         <v>-4.0945</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5414</v>
+        <v>-4.0689</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3474</v>
+        <v>-3.8481</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.194</v>
+        <v>-0.2208</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3126</v>
@@ -2092,13 +2092,13 @@
         <v>1.9301</v>
       </c>
       <c r="S21" t="n">
-        <v>1.6148</v>
+        <v>1.0873</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9915</v>
+        <v>0.4908</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6233</v>
+        <v>0.5965</v>
       </c>
       <c r="V21" t="n">
         <v>-3.8087</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.2579</v>
+        <v>-4.8483</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.2704</v>
+        <v>-5.3692</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0125</v>
+        <v>0.5208</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3324</v>
@@ -2170,13 +2170,13 @@
         <v>2.1231</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.5322</v>
+        <v>-0.1226</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1157</v>
+        <v>-0.2145</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4164</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6562</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.815600000000001</v>
+        <v>-4.148</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.196400000000001</v>
+        <v>-3.196700000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6189</v>
+        <v>-0.9512999999999997</v>
       </c>
       <c r="G23" t="n">
         <v>4.105</v>
@@ -2248,13 +2248,13 @@
         <v>13.5106</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2652</v>
+        <v>3.932900000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1259000000000001</v>
+        <v>0.1259</v>
       </c>
       <c r="U23" t="n">
-        <v>3.1395</v>
+        <v>3.8071</v>
       </c>
       <c r="V23" t="n">
         <v>-11.2206</v>
